--- a/marketing_report/outputs/Cursos/tabla_utm_campaigns.xlsx
+++ b/marketing_report/outputs/Cursos/tabla_utm_campaigns.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -40,49 +40,19 @@
     <t>Tasa_Conversion_%</t>
   </si>
   <si>
+    <t>120235998797960048</t>
+  </si>
+  <si>
+    <t>14876203835</t>
+  </si>
+  <si>
     <t>21676468921</t>
   </si>
   <si>
-    <t>14876203835</t>
-  </si>
-  <si>
     <t>carreras</t>
   </si>
   <si>
-    <t>23084310717</t>
-  </si>
-  <si>
-    <t>8419948319</t>
-  </si>
-  <si>
-    <t>organic</t>
-  </si>
-  <si>
-    <t>14875022827</t>
-  </si>
-  <si>
-    <t>14909096324</t>
-  </si>
-  <si>
-    <t>120235998797960048</t>
-  </si>
-  <si>
-    <t>14896121927</t>
-  </si>
-  <si>
-    <t>14909223761</t>
-  </si>
-  <si>
-    <t>15357460006</t>
-  </si>
-  <si>
-    <t>19230946036</t>
-  </si>
-  <si>
-    <t>20612364611</t>
-  </si>
-  <si>
-    <t>23277494379</t>
+    <t>ig</t>
   </si>
   <si>
     <t>googleads</t>
@@ -91,22 +61,13 @@
     <t>facebook</t>
   </si>
   <si>
-    <t>instagram</t>
-  </si>
-  <si>
-    <t>ig</t>
+    <t>paid</t>
   </si>
   <si>
     <t>leads</t>
   </si>
   <si>
-    <t>leadads</t>
-  </si>
-  <si>
-    <t>feed</t>
-  </si>
-  <si>
-    <t>paid</t>
+    <t>alcance</t>
   </si>
 </sst>
 </file>
@@ -464,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -498,22 +459,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -524,22 +485,22 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -550,22 +511,22 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -576,307 +537,24 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
         <v>100</v>
       </c>
     </row>
